--- a/Data/Data ST/DATA ST.xlsx
+++ b/Data/Data ST/DATA ST.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Drive của tôi\Report\Đối chiếu xuất hàng\Data\Data ST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3B93A6C-255E-43BB-AF6A-8AEE56538240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B359ED59-2F4F-4BDB-96DE-752401F080F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B7395079-1554-47B3-B515-E3FF218604C2}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="430">
   <si>
     <t>Nơi nhận</t>
   </si>
@@ -1279,6 +1279,42 @@
   </si>
   <si>
     <t>A218</t>
+  </si>
+  <si>
+    <t>KFM_HCM_TBI - 289 Hồng Lạc</t>
+  </si>
+  <si>
+    <t>A210</t>
+  </si>
+  <si>
+    <t>KFM_BDU_TAN - 13 Vĩnh Phú 41</t>
+  </si>
+  <si>
+    <t>A214</t>
+  </si>
+  <si>
+    <t>KFM_HCM_PNH - 29 Đặng Văn Ngữ</t>
+  </si>
+  <si>
+    <t>A223</t>
+  </si>
+  <si>
+    <t>KFM_HCM_GVA - 8 Nguyễn Văn Dung</t>
+  </si>
+  <si>
+    <t>A224</t>
+  </si>
+  <si>
+    <t>KFM_HCM_TDU - 96K Đường Số 12 Tam Bình</t>
+  </si>
+  <si>
+    <t>A225</t>
+  </si>
+  <si>
+    <t>KFM_BDU_DAN - 145B Lê Trọng Tấn</t>
+  </si>
+  <si>
+    <t>A209</t>
   </si>
 </sst>
 </file>
@@ -1372,9 +1408,15 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1689,7 +1731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC62C01-890F-434E-8057-CC64EDC780A7}">
-  <dimension ref="A1:B220"/>
+  <dimension ref="A1:B226"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="52.54296875" bestFit="1" customWidth="1"/>
@@ -3456,6 +3498,54 @@
         <v>417</v>
       </c>
     </row>
+    <row r="221" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A221" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B221" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A222" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A223" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A224" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A225" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A226" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
